--- a/DBs/nfl/Results/NFL_2019_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2019_Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TracerProjects2\NFL_Elo\Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\nfl\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CA4C351-AE98-4A0F-834C-3A1C84E31348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B863E8B9-8000-4BF3-B090-556C07D8CDCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{304F7FAA-8920-4BC1-AEDA-7A2DE7D7BF14}"/>
   </bookViews>
@@ -82,9 +82,6 @@
     <t>NYJ</t>
   </si>
   <si>
-    <t>STL</t>
-  </si>
-  <si>
     <t>CAR</t>
   </si>
   <si>
@@ -116,9 +113,6 @@
   </si>
   <si>
     <t>CIN</t>
-  </si>
-  <si>
-    <t>SD</t>
   </si>
   <si>
     <t>IND</t>
@@ -176,6 +170,12 @@
   </si>
   <si>
     <t>N</t>
+  </si>
+  <si>
+    <t>LAR</t>
+  </si>
+  <si>
+    <t>LAC</t>
   </si>
 </sst>
 </file>
@@ -1261,10 +1261,10 @@
         <v>11</v>
       </c>
       <c r="E8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s">
         <v>20</v>
-      </c>
-      <c r="F8" t="s">
-        <v>21</v>
       </c>
       <c r="G8" t="s">
         <v>14</v>
@@ -1293,10 +1293,10 @@
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G9" t="s">
         <v>15</v>
@@ -1325,10 +1325,10 @@
         <v>11</v>
       </c>
       <c r="E10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" t="s">
         <v>22</v>
-      </c>
-      <c r="F10" t="s">
-        <v>23</v>
       </c>
       <c r="G10" t="s">
         <v>14</v>
@@ -1357,10 +1357,10 @@
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
@@ -1389,10 +1389,10 @@
         <v>11</v>
       </c>
       <c r="E12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" t="s">
         <v>24</v>
-      </c>
-      <c r="F12" t="s">
-        <v>25</v>
       </c>
       <c r="G12" t="s">
         <v>14</v>
@@ -1421,10 +1421,10 @@
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
@@ -1453,10 +1453,10 @@
         <v>11</v>
       </c>
       <c r="E14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" t="s">
         <v>26</v>
-      </c>
-      <c r="F14" t="s">
-        <v>27</v>
       </c>
       <c r="G14" t="s">
         <v>14</v>
@@ -1485,10 +1485,10 @@
         <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>
@@ -1517,10 +1517,10 @@
         <v>11</v>
       </c>
       <c r="E16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" t="s">
         <v>28</v>
-      </c>
-      <c r="F16" t="s">
-        <v>29</v>
       </c>
       <c r="G16" t="s">
         <v>15</v>
@@ -1549,10 +1549,10 @@
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G17" t="s">
         <v>14</v>
@@ -1581,10 +1581,10 @@
         <v>11</v>
       </c>
       <c r="E18" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" t="s">
         <v>30</v>
-      </c>
-      <c r="F18" t="s">
-        <v>31</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
@@ -1613,10 +1613,10 @@
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G19" t="s">
         <v>14</v>
@@ -1645,10 +1645,10 @@
         <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G20" t="s">
         <v>15</v>
@@ -1677,10 +1677,10 @@
         <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G21" t="s">
         <v>14</v>
@@ -1709,10 +1709,10 @@
         <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F22" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G22" t="s">
         <v>14</v>
@@ -1741,10 +1741,10 @@
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
@@ -1773,10 +1773,10 @@
         <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G24" t="s">
         <v>15</v>
@@ -1805,10 +1805,10 @@
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G25" t="s">
         <v>14</v>
@@ -1837,10 +1837,10 @@
         <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G26" t="s">
         <v>14</v>
@@ -1869,10 +1869,10 @@
         <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F27" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G27" t="s">
         <v>15</v>
@@ -1901,10 +1901,10 @@
         <v>11</v>
       </c>
       <c r="E28" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F28" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G28" t="s">
         <v>15</v>
@@ -1933,10 +1933,10 @@
         <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G29" t="s">
         <v>14</v>
@@ -1965,10 +1965,10 @@
         <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G30" t="s">
         <v>15</v>
@@ -1997,10 +1997,10 @@
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F31" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G31" t="s">
         <v>14</v>
@@ -2029,10 +2029,10 @@
         <v>11</v>
       </c>
       <c r="E32" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F32" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G32" t="s">
         <v>15</v>
@@ -2061,10 +2061,10 @@
         <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F33" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G33" t="s">
         <v>14</v>
@@ -2093,10 +2093,10 @@
         <v>11</v>
       </c>
       <c r="E34" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G34" t="s">
         <v>14</v>
@@ -2125,10 +2125,10 @@
         <v>11</v>
       </c>
       <c r="E35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F35" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G35" t="s">
         <v>15</v>
@@ -2160,7 +2160,7 @@
         <v>18</v>
       </c>
       <c r="F36" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G36" t="s">
         <v>14</v>
@@ -2189,7 +2189,7 @@
         <v>11</v>
       </c>
       <c r="E37" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F37" t="s">
         <v>18</v>
@@ -2221,10 +2221,10 @@
         <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G38" t="s">
         <v>14</v>
@@ -2253,10 +2253,10 @@
         <v>11</v>
       </c>
       <c r="E39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F39" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G39" t="s">
         <v>15</v>
@@ -2285,10 +2285,10 @@
         <v>11</v>
       </c>
       <c r="E40" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G40" t="s">
         <v>14</v>
@@ -2317,10 +2317,10 @@
         <v>11</v>
       </c>
       <c r="E41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F41" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G41" t="s">
         <v>15</v>
@@ -2349,10 +2349,10 @@
         <v>11</v>
       </c>
       <c r="E42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F42" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G42" t="s">
         <v>15</v>
@@ -2381,10 +2381,10 @@
         <v>11</v>
       </c>
       <c r="E43" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G43" t="s">
         <v>14</v>
@@ -2413,10 +2413,10 @@
         <v>11</v>
       </c>
       <c r="E44" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G44" t="s">
         <v>14</v>
@@ -2445,10 +2445,10 @@
         <v>11</v>
       </c>
       <c r="E45" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F45" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G45" t="s">
         <v>15</v>
@@ -2477,10 +2477,10 @@
         <v>11</v>
       </c>
       <c r="E46" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F46" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G46" t="s">
         <v>15</v>
@@ -2509,10 +2509,10 @@
         <v>11</v>
       </c>
       <c r="E47" t="s">
+        <v>51</v>
+      </c>
+      <c r="F47" t="s">
         <v>32</v>
-      </c>
-      <c r="F47" t="s">
-        <v>34</v>
       </c>
       <c r="G47" t="s">
         <v>14</v>
@@ -2605,10 +2605,10 @@
         <v>11</v>
       </c>
       <c r="E50" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F50" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G50" t="s">
         <v>15</v>
@@ -2637,10 +2637,10 @@
         <v>11</v>
       </c>
       <c r="E51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F51" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G51" t="s">
         <v>14</v>
@@ -2669,10 +2669,10 @@
         <v>11</v>
       </c>
       <c r="E52" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F52" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G52" t="s">
         <v>14</v>
@@ -2701,10 +2701,10 @@
         <v>11</v>
       </c>
       <c r="E53" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F53" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G53" t="s">
         <v>15</v>
@@ -2733,10 +2733,10 @@
         <v>11</v>
       </c>
       <c r="E54" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F54" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G54" t="s">
         <v>14</v>
@@ -2765,10 +2765,10 @@
         <v>11</v>
       </c>
       <c r="E55" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F55" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G55" t="s">
         <v>15</v>
@@ -2797,10 +2797,10 @@
         <v>11</v>
       </c>
       <c r="E56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F56" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G56" t="s">
         <v>14</v>
@@ -2829,10 +2829,10 @@
         <v>11</v>
       </c>
       <c r="E57" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F57" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G57" t="s">
         <v>15</v>
@@ -2864,7 +2864,7 @@
         <v>13</v>
       </c>
       <c r="F58" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G58" t="s">
         <v>14</v>
@@ -2893,7 +2893,7 @@
         <v>11</v>
       </c>
       <c r="E59" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F59" t="s">
         <v>13</v>
@@ -2925,10 +2925,10 @@
         <v>11</v>
       </c>
       <c r="E60" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F60" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G60" t="s">
         <v>15</v>
@@ -2957,10 +2957,10 @@
         <v>11</v>
       </c>
       <c r="E61" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F61" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G61" t="s">
         <v>14</v>
@@ -2992,7 +2992,7 @@
         <v>17</v>
       </c>
       <c r="F62" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G62" t="s">
         <v>15</v>
@@ -3021,7 +3021,7 @@
         <v>11</v>
       </c>
       <c r="E63" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F63" t="s">
         <v>17</v>
@@ -3053,7 +3053,7 @@
         <v>11</v>
       </c>
       <c r="E64" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F64" t="s">
         <v>19</v>
@@ -3088,7 +3088,7 @@
         <v>19</v>
       </c>
       <c r="F65" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G65" t="s">
         <v>15</v>
@@ -3117,10 +3117,10 @@
         <v>11</v>
       </c>
       <c r="E66" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F66" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G66" t="s">
         <v>15</v>
@@ -3149,10 +3149,10 @@
         <v>11</v>
       </c>
       <c r="E67" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F67" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G67" t="s">
         <v>14</v>
@@ -3181,7 +3181,7 @@
         <v>11</v>
       </c>
       <c r="E68" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F68" t="s">
         <v>17</v>
@@ -3216,7 +3216,7 @@
         <v>17</v>
       </c>
       <c r="F69" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G69" t="s">
         <v>14</v>
@@ -3248,7 +3248,7 @@
         <v>18</v>
       </c>
       <c r="F70" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G70" t="s">
         <v>15</v>
@@ -3277,7 +3277,7 @@
         <v>11</v>
       </c>
       <c r="E71" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F71" t="s">
         <v>18</v>
@@ -3309,10 +3309,10 @@
         <v>11</v>
       </c>
       <c r="E72" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F72" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G72" t="s">
         <v>15</v>
@@ -3341,10 +3341,10 @@
         <v>11</v>
       </c>
       <c r="E73" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F73" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G73" t="s">
         <v>14</v>
@@ -3376,7 +3376,7 @@
         <v>12</v>
       </c>
       <c r="F74" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G74" t="s">
         <v>15</v>
@@ -3405,7 +3405,7 @@
         <v>11</v>
       </c>
       <c r="E75" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F75" t="s">
         <v>12</v>
@@ -3437,10 +3437,10 @@
         <v>11</v>
       </c>
       <c r="E76" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F76" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G76" t="s">
         <v>14</v>
@@ -3469,10 +3469,10 @@
         <v>11</v>
       </c>
       <c r="E77" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F77" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G77" t="s">
         <v>15</v>
@@ -3501,10 +3501,10 @@
         <v>11</v>
       </c>
       <c r="E78" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F78" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G78" t="s">
         <v>15</v>
@@ -3533,10 +3533,10 @@
         <v>11</v>
       </c>
       <c r="E79" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F79" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G79" t="s">
         <v>14</v>
@@ -3568,7 +3568,7 @@
         <v>16</v>
       </c>
       <c r="F80" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G80" t="s">
         <v>15</v>
@@ -3597,7 +3597,7 @@
         <v>11</v>
       </c>
       <c r="E81" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F81" t="s">
         <v>16</v>
@@ -3629,7 +3629,7 @@
         <v>11</v>
       </c>
       <c r="E82" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F82" t="s">
         <v>19</v>
@@ -3664,7 +3664,7 @@
         <v>19</v>
       </c>
       <c r="F83" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G83" t="s">
         <v>14</v>
@@ -3693,10 +3693,10 @@
         <v>11</v>
       </c>
       <c r="E84" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F84" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G84" t="s">
         <v>14</v>
@@ -3725,10 +3725,10 @@
         <v>11</v>
       </c>
       <c r="E85" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F85" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G85" t="s">
         <v>15</v>
@@ -3757,10 +3757,10 @@
         <v>11</v>
       </c>
       <c r="E86" t="s">
+        <v>35</v>
+      </c>
+      <c r="F86" t="s">
         <v>37</v>
-      </c>
-      <c r="F86" t="s">
-        <v>39</v>
       </c>
       <c r="G86" t="s">
         <v>14</v>
@@ -3789,10 +3789,10 @@
         <v>11</v>
       </c>
       <c r="E87" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F87" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G87" t="s">
         <v>15</v>
@@ -3821,10 +3821,10 @@
         <v>11</v>
       </c>
       <c r="E88" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F88" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G88" t="s">
         <v>14</v>
@@ -3853,10 +3853,10 @@
         <v>11</v>
       </c>
       <c r="E89" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F89" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G89" t="s">
         <v>15</v>
@@ -3885,10 +3885,10 @@
         <v>11</v>
       </c>
       <c r="E90" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F90" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G90" t="s">
         <v>14</v>
@@ -3917,10 +3917,10 @@
         <v>11</v>
       </c>
       <c r="E91" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F91" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G91" t="s">
         <v>15</v>
@@ -3949,10 +3949,10 @@
         <v>11</v>
       </c>
       <c r="E92" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F92" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G92" t="s">
         <v>15</v>
@@ -3981,10 +3981,10 @@
         <v>11</v>
       </c>
       <c r="E93" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F93" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G93" t="s">
         <v>14</v>
@@ -4013,10 +4013,10 @@
         <v>11</v>
       </c>
       <c r="E94" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F94" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G94" t="s">
         <v>14</v>
@@ -4045,10 +4045,10 @@
         <v>11</v>
       </c>
       <c r="E95" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F95" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G95" t="s">
         <v>15</v>
@@ -4080,7 +4080,7 @@
         <v>13</v>
       </c>
       <c r="F96" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G96" t="s">
         <v>14</v>
@@ -4109,7 +4109,7 @@
         <v>11</v>
       </c>
       <c r="E97" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F97" t="s">
         <v>13</v>
@@ -4141,7 +4141,7 @@
         <v>11</v>
       </c>
       <c r="E98" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F98" t="s">
         <v>12</v>
@@ -4176,7 +4176,7 @@
         <v>12</v>
       </c>
       <c r="F99" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G99" t="s">
         <v>15</v>
@@ -4205,7 +4205,7 @@
         <v>11</v>
       </c>
       <c r="E100" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F100" t="s">
         <v>17</v>
@@ -4240,7 +4240,7 @@
         <v>17</v>
       </c>
       <c r="F101" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G101" t="s">
         <v>15</v>
@@ -4269,7 +4269,7 @@
         <v>11</v>
       </c>
       <c r="E102" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F102" t="s">
         <v>18</v>
@@ -4304,7 +4304,7 @@
         <v>18</v>
       </c>
       <c r="F103" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G103" t="s">
         <v>15</v>
@@ -4333,10 +4333,10 @@
         <v>11</v>
       </c>
       <c r="E104" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F104" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G104" t="s">
         <v>14</v>
@@ -4365,10 +4365,10 @@
         <v>11</v>
       </c>
       <c r="E105" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F105" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G105" t="s">
         <v>15</v>
@@ -4397,10 +4397,10 @@
         <v>11</v>
       </c>
       <c r="E106" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F106" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G106" t="s">
         <v>14</v>
@@ -4429,10 +4429,10 @@
         <v>11</v>
       </c>
       <c r="E107" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F107" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G107" t="s">
         <v>15</v>
@@ -4461,10 +4461,10 @@
         <v>11</v>
       </c>
       <c r="E108" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F108" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G108" t="s">
         <v>14</v>
@@ -4493,10 +4493,10 @@
         <v>11</v>
       </c>
       <c r="E109" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F109" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G109" t="s">
         <v>15</v>
@@ -4525,10 +4525,10 @@
         <v>11</v>
       </c>
       <c r="E110" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F110" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G110" t="s">
         <v>14</v>
@@ -4557,10 +4557,10 @@
         <v>11</v>
       </c>
       <c r="E111" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F111" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G111" t="s">
         <v>15</v>
@@ -4589,10 +4589,10 @@
         <v>11</v>
       </c>
       <c r="E112" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F112" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G112" t="s">
         <v>14</v>
@@ -4621,10 +4621,10 @@
         <v>11</v>
       </c>
       <c r="E113" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F113" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G113" t="s">
         <v>15</v>
@@ -4653,10 +4653,10 @@
         <v>11</v>
       </c>
       <c r="E114" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F114" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G114" t="s">
         <v>15</v>
@@ -4685,10 +4685,10 @@
         <v>11</v>
       </c>
       <c r="E115" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F115" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G115" t="s">
         <v>14</v>
@@ -4717,10 +4717,10 @@
         <v>11</v>
       </c>
       <c r="E116" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F116" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G116" t="s">
         <v>14</v>
@@ -4749,10 +4749,10 @@
         <v>11</v>
       </c>
       <c r="E117" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F117" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G117" t="s">
         <v>15</v>
@@ -4781,10 +4781,10 @@
         <v>11</v>
       </c>
       <c r="E118" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F118" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G118" t="s">
         <v>14</v>
@@ -4813,10 +4813,10 @@
         <v>11</v>
       </c>
       <c r="E119" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F119" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G119" t="s">
         <v>15</v>
@@ -4909,10 +4909,10 @@
         <v>11</v>
       </c>
       <c r="E122" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F122" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G122" t="s">
         <v>14</v>
@@ -4941,10 +4941,10 @@
         <v>11</v>
       </c>
       <c r="E123" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F123" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G123" t="s">
         <v>15</v>
@@ -4973,10 +4973,10 @@
         <v>11</v>
       </c>
       <c r="E124" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F124" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G124" t="s">
         <v>15</v>
@@ -5005,10 +5005,10 @@
         <v>11</v>
       </c>
       <c r="E125" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F125" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G125" t="s">
         <v>14</v>
@@ -5037,10 +5037,10 @@
         <v>11</v>
       </c>
       <c r="E126" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F126" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G126" t="s">
         <v>15</v>
@@ -5069,10 +5069,10 @@
         <v>11</v>
       </c>
       <c r="E127" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F127" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G127" t="s">
         <v>14</v>
@@ -5101,10 +5101,10 @@
         <v>11</v>
       </c>
       <c r="E128" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F128" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G128" t="s">
         <v>15</v>
@@ -5133,10 +5133,10 @@
         <v>11</v>
       </c>
       <c r="E129" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F129" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G129" t="s">
         <v>14</v>
@@ -5165,7 +5165,7 @@
         <v>11</v>
       </c>
       <c r="E130" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F130" t="s">
         <v>19</v>
@@ -5200,7 +5200,7 @@
         <v>19</v>
       </c>
       <c r="F131" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G131" t="s">
         <v>14</v>
@@ -5229,7 +5229,7 @@
         <v>11</v>
       </c>
       <c r="E132" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F132" t="s">
         <v>17</v>
@@ -5264,7 +5264,7 @@
         <v>17</v>
       </c>
       <c r="F133" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G133" t="s">
         <v>14</v>
@@ -5296,7 +5296,7 @@
         <v>18</v>
       </c>
       <c r="F134" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G134" t="s">
         <v>14</v>
@@ -5325,7 +5325,7 @@
         <v>11</v>
       </c>
       <c r="E135" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F135" t="s">
         <v>18</v>
@@ -5357,10 +5357,10 @@
         <v>11</v>
       </c>
       <c r="E136" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F136" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G136" t="s">
         <v>15</v>
@@ -5389,10 +5389,10 @@
         <v>11</v>
       </c>
       <c r="E137" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F137" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G137" t="s">
         <v>14</v>
@@ -5421,7 +5421,7 @@
         <v>11</v>
       </c>
       <c r="E138" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F138" t="s">
         <v>13</v>
@@ -5456,7 +5456,7 @@
         <v>13</v>
       </c>
       <c r="F139" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G139" t="s">
         <v>14</v>
@@ -5485,10 +5485,10 @@
         <v>11</v>
       </c>
       <c r="E140" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F140" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G140" t="s">
         <v>14</v>
@@ -5517,10 +5517,10 @@
         <v>11</v>
       </c>
       <c r="E141" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F141" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G141" t="s">
         <v>15</v>
@@ -5552,7 +5552,7 @@
         <v>16</v>
       </c>
       <c r="F142" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G142" t="s">
         <v>14</v>
@@ -5581,7 +5581,7 @@
         <v>11</v>
       </c>
       <c r="E143" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F143" t="s">
         <v>16</v>
@@ -5613,10 +5613,10 @@
         <v>11</v>
       </c>
       <c r="E144" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F144" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G144" t="s">
         <v>15</v>
@@ -5645,10 +5645,10 @@
         <v>11</v>
       </c>
       <c r="E145" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F145" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G145" t="s">
         <v>14</v>
@@ -5677,10 +5677,10 @@
         <v>11</v>
       </c>
       <c r="E146" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F146" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G146" t="s">
         <v>14</v>
@@ -5709,10 +5709,10 @@
         <v>11</v>
       </c>
       <c r="E147" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F147" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G147" t="s">
         <v>15</v>
@@ -5741,10 +5741,10 @@
         <v>11</v>
       </c>
       <c r="E148" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F148" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G148" t="s">
         <v>14</v>
@@ -5773,10 +5773,10 @@
         <v>11</v>
       </c>
       <c r="E149" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F149" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G149" t="s">
         <v>15</v>
@@ -5805,10 +5805,10 @@
         <v>11</v>
       </c>
       <c r="E150" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F150" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G150" t="s">
         <v>14</v>
@@ -5837,10 +5837,10 @@
         <v>11</v>
       </c>
       <c r="E151" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F151" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G151" t="s">
         <v>15</v>
@@ -5872,7 +5872,7 @@
         <v>12</v>
       </c>
       <c r="F152" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G152" t="s">
         <v>14</v>
@@ -5901,7 +5901,7 @@
         <v>11</v>
       </c>
       <c r="E153" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F153" t="s">
         <v>12</v>
@@ -5933,10 +5933,10 @@
         <v>11</v>
       </c>
       <c r="E154" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F154" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G154" t="s">
         <v>14</v>
@@ -5965,10 +5965,10 @@
         <v>11</v>
       </c>
       <c r="E155" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F155" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G155" t="s">
         <v>15</v>
@@ -5997,10 +5997,10 @@
         <v>11</v>
       </c>
       <c r="E156" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F156" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G156" t="s">
         <v>15</v>
@@ -6029,10 +6029,10 @@
         <v>11</v>
       </c>
       <c r="E157" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F157" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G157" t="s">
         <v>14</v>
@@ -6061,10 +6061,10 @@
         <v>11</v>
       </c>
       <c r="E158" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F158" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G158" t="s">
         <v>15</v>
@@ -6093,10 +6093,10 @@
         <v>11</v>
       </c>
       <c r="E159" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F159" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G159" t="s">
         <v>14</v>
@@ -6125,10 +6125,10 @@
         <v>11</v>
       </c>
       <c r="E160" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F160" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G160" t="s">
         <v>14</v>
@@ -6157,10 +6157,10 @@
         <v>11</v>
       </c>
       <c r="E161" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F161" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G161" t="s">
         <v>15</v>
@@ -6189,10 +6189,10 @@
         <v>11</v>
       </c>
       <c r="E162" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F162" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G162" t="s">
         <v>14</v>
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="E163" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F163" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G163" t="s">
         <v>15</v>
@@ -6253,10 +6253,10 @@
         <v>11</v>
       </c>
       <c r="E164" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F164" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G164" t="s">
         <v>15</v>
@@ -6285,10 +6285,10 @@
         <v>11</v>
       </c>
       <c r="E165" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F165" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G165" t="s">
         <v>14</v>
@@ -6317,10 +6317,10 @@
         <v>11</v>
       </c>
       <c r="E166" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F166" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G166" t="s">
         <v>14</v>
@@ -6349,10 +6349,10 @@
         <v>11</v>
       </c>
       <c r="E167" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F167" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G167" t="s">
         <v>15</v>
@@ -6381,10 +6381,10 @@
         <v>11</v>
       </c>
       <c r="E168" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F168" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G168" t="s">
         <v>14</v>
@@ -6413,10 +6413,10 @@
         <v>11</v>
       </c>
       <c r="E169" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F169" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G169" t="s">
         <v>15</v>
@@ -6445,10 +6445,10 @@
         <v>11</v>
       </c>
       <c r="E170" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F170" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G170" t="s">
         <v>14</v>
@@ -6477,10 +6477,10 @@
         <v>11</v>
       </c>
       <c r="E171" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F171" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G171" t="s">
         <v>15</v>
@@ -6512,7 +6512,7 @@
         <v>16</v>
       </c>
       <c r="F172" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G172" t="s">
         <v>15</v>
@@ -6541,7 +6541,7 @@
         <v>11</v>
       </c>
       <c r="E173" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F173" t="s">
         <v>16</v>
@@ -6573,7 +6573,7 @@
         <v>11</v>
       </c>
       <c r="E174" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F174" t="s">
         <v>17</v>
@@ -6608,7 +6608,7 @@
         <v>17</v>
       </c>
       <c r="F175" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G175" t="s">
         <v>14</v>
@@ -6637,10 +6637,10 @@
         <v>11</v>
       </c>
       <c r="E176" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F176" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G176" t="s">
         <v>14</v>
@@ -6669,10 +6669,10 @@
         <v>11</v>
       </c>
       <c r="E177" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F177" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G177" t="s">
         <v>15</v>
@@ -6704,7 +6704,7 @@
         <v>19</v>
       </c>
       <c r="F178" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G178" t="s">
         <v>15</v>
@@ -6733,7 +6733,7 @@
         <v>11</v>
       </c>
       <c r="E179" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F179" t="s">
         <v>19</v>
@@ -6765,10 +6765,10 @@
         <v>11</v>
       </c>
       <c r="E180" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F180" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G180" t="s">
         <v>15</v>
@@ -6797,10 +6797,10 @@
         <v>11</v>
       </c>
       <c r="E181" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F181" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G181" t="s">
         <v>14</v>
@@ -6829,10 +6829,10 @@
         <v>11</v>
       </c>
       <c r="E182" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F182" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G182" t="s">
         <v>14</v>
@@ -6861,10 +6861,10 @@
         <v>11</v>
       </c>
       <c r="E183" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F183" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G183" t="s">
         <v>15</v>
@@ -6896,7 +6896,7 @@
         <v>12</v>
       </c>
       <c r="F184" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G184" t="s">
         <v>15</v>
@@ -6925,7 +6925,7 @@
         <v>11</v>
       </c>
       <c r="E185" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F185" t="s">
         <v>12</v>
@@ -6957,10 +6957,10 @@
         <v>11</v>
       </c>
       <c r="E186" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F186" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G186" t="s">
         <v>14</v>
@@ -6989,10 +6989,10 @@
         <v>11</v>
       </c>
       <c r="E187" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F187" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G187" t="s">
         <v>15</v>
@@ -7024,7 +7024,7 @@
         <v>18</v>
       </c>
       <c r="F188" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G188" t="s">
         <v>15</v>
@@ -7053,7 +7053,7 @@
         <v>11</v>
       </c>
       <c r="E189" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F189" t="s">
         <v>18</v>
@@ -7085,10 +7085,10 @@
         <v>11</v>
       </c>
       <c r="E190" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F190" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G190" t="s">
         <v>15</v>
@@ -7117,10 +7117,10 @@
         <v>11</v>
       </c>
       <c r="E191" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F191" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G191" t="s">
         <v>14</v>
@@ -7152,7 +7152,7 @@
         <v>16</v>
       </c>
       <c r="F192" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G192" t="s">
         <v>14</v>
@@ -7181,7 +7181,7 @@
         <v>11</v>
       </c>
       <c r="E193" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F193" t="s">
         <v>16</v>
@@ -7213,10 +7213,10 @@
         <v>11</v>
       </c>
       <c r="E194" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F194" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G194" t="s">
         <v>14</v>
@@ -7245,10 +7245,10 @@
         <v>11</v>
       </c>
       <c r="E195" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F195" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G195" t="s">
         <v>15</v>
@@ -7277,7 +7277,7 @@
         <v>11</v>
       </c>
       <c r="E196" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F196" t="s">
         <v>17</v>
@@ -7312,7 +7312,7 @@
         <v>17</v>
       </c>
       <c r="F197" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G197" t="s">
         <v>15</v>
@@ -7341,10 +7341,10 @@
         <v>11</v>
       </c>
       <c r="E198" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F198" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G198" t="s">
         <v>14</v>
@@ -7373,10 +7373,10 @@
         <v>11</v>
       </c>
       <c r="E199" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F199" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G199" t="s">
         <v>15</v>
@@ -7405,10 +7405,10 @@
         <v>11</v>
       </c>
       <c r="E200" t="s">
+        <v>33</v>
+      </c>
+      <c r="F200" t="s">
         <v>35</v>
-      </c>
-      <c r="F200" t="s">
-        <v>37</v>
       </c>
       <c r="G200" t="s">
         <v>14</v>
@@ -7437,10 +7437,10 @@
         <v>11</v>
       </c>
       <c r="E201" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F201" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G201" t="s">
         <v>15</v>
@@ -7472,7 +7472,7 @@
         <v>12</v>
       </c>
       <c r="F202" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G202" t="s">
         <v>15</v>
@@ -7501,7 +7501,7 @@
         <v>11</v>
       </c>
       <c r="E203" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F203" t="s">
         <v>12</v>
@@ -7533,10 +7533,10 @@
         <v>11</v>
       </c>
       <c r="E204" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F204" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G204" t="s">
         <v>15</v>
@@ -7565,10 +7565,10 @@
         <v>11</v>
       </c>
       <c r="E205" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F205" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G205" t="s">
         <v>14</v>
@@ -7597,7 +7597,7 @@
         <v>11</v>
       </c>
       <c r="E206" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F206" t="s">
         <v>13</v>
@@ -7632,7 +7632,7 @@
         <v>13</v>
       </c>
       <c r="F207" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G207" t="s">
         <v>15</v>
@@ -7661,10 +7661,10 @@
         <v>11</v>
       </c>
       <c r="E208" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F208" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G208" t="s">
         <v>14</v>
@@ -7693,10 +7693,10 @@
         <v>11</v>
       </c>
       <c r="E209" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F209" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G209" t="s">
         <v>15</v>
@@ -7725,10 +7725,10 @@
         <v>11</v>
       </c>
       <c r="E210" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F210" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G210" t="s">
         <v>15</v>
@@ -7757,10 +7757,10 @@
         <v>11</v>
       </c>
       <c r="E211" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F211" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G211" t="s">
         <v>14</v>
@@ -7789,7 +7789,7 @@
         <v>11</v>
       </c>
       <c r="E212" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F212" t="s">
         <v>19</v>
@@ -7824,7 +7824,7 @@
         <v>19</v>
       </c>
       <c r="F213" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G213" t="s">
         <v>15</v>
@@ -7856,7 +7856,7 @@
         <v>16</v>
       </c>
       <c r="F214" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G214" t="s">
         <v>15</v>
@@ -7885,7 +7885,7 @@
         <v>11</v>
       </c>
       <c r="E215" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F215" t="s">
         <v>16</v>
@@ -7917,7 +7917,7 @@
         <v>11</v>
       </c>
       <c r="E216" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F216" t="s">
         <v>18</v>
@@ -7952,7 +7952,7 @@
         <v>18</v>
       </c>
       <c r="F217" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G217" t="s">
         <v>15</v>
@@ -7981,7 +7981,7 @@
         <v>11</v>
       </c>
       <c r="E218" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F218" t="s">
         <v>13</v>
@@ -8016,7 +8016,7 @@
         <v>13</v>
       </c>
       <c r="F219" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G219" t="s">
         <v>15</v>
@@ -8045,10 +8045,10 @@
         <v>11</v>
       </c>
       <c r="E220" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F220" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G220" t="s">
         <v>15</v>
@@ -8077,10 +8077,10 @@
         <v>11</v>
       </c>
       <c r="E221" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F221" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G221" t="s">
         <v>14</v>
@@ -8109,10 +8109,10 @@
         <v>11</v>
       </c>
       <c r="E222" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F222" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G222" t="s">
         <v>15</v>
@@ -8141,10 +8141,10 @@
         <v>11</v>
       </c>
       <c r="E223" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F223" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G223" t="s">
         <v>14</v>
@@ -8173,7 +8173,7 @@
         <v>11</v>
       </c>
       <c r="E224" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F224" t="s">
         <v>17</v>
@@ -8208,7 +8208,7 @@
         <v>17</v>
       </c>
       <c r="F225" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G225" t="s">
         <v>15</v>
@@ -8237,10 +8237,10 @@
         <v>11</v>
       </c>
       <c r="E226" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F226" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G226" t="s">
         <v>15</v>
@@ -8269,10 +8269,10 @@
         <v>11</v>
       </c>
       <c r="E227" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F227" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G227" t="s">
         <v>14</v>
@@ -8301,10 +8301,10 @@
         <v>11</v>
       </c>
       <c r="E228" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F228" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G228" t="s">
         <v>15</v>
@@ -8333,10 +8333,10 @@
         <v>11</v>
       </c>
       <c r="E229" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F229" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G229" t="s">
         <v>14</v>
@@ -8365,7 +8365,7 @@
         <v>11</v>
       </c>
       <c r="E230" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F230" t="s">
         <v>19</v>
@@ -8400,7 +8400,7 @@
         <v>19</v>
       </c>
       <c r="F231" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G231" t="s">
         <v>14</v>
@@ -8429,10 +8429,10 @@
         <v>11</v>
       </c>
       <c r="E232" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F232" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G232" t="s">
         <v>15</v>
@@ -8461,10 +8461,10 @@
         <v>11</v>
       </c>
       <c r="E233" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F233" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G233" t="s">
         <v>14</v>
@@ -8493,10 +8493,10 @@
         <v>11</v>
       </c>
       <c r="E234" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F234" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G234" t="s">
         <v>15</v>
@@ -8525,10 +8525,10 @@
         <v>11</v>
       </c>
       <c r="E235" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F235" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G235" t="s">
         <v>14</v>
@@ -8557,10 +8557,10 @@
         <v>11</v>
       </c>
       <c r="E236" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F236" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G236" t="s">
         <v>15</v>
@@ -8589,10 +8589,10 @@
         <v>11</v>
       </c>
       <c r="E237" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F237" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G237" t="s">
         <v>14</v>
@@ -8621,10 +8621,10 @@
         <v>11</v>
       </c>
       <c r="E238" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F238" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G238" t="s">
         <v>15</v>
@@ -8653,10 +8653,10 @@
         <v>11</v>
       </c>
       <c r="E239" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F239" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G239" t="s">
         <v>14</v>
@@ -8688,7 +8688,7 @@
         <v>12</v>
       </c>
       <c r="F240" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G240" t="s">
         <v>14</v>
@@ -8717,7 +8717,7 @@
         <v>11</v>
       </c>
       <c r="E241" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F241" t="s">
         <v>12</v>
@@ -8749,10 +8749,10 @@
         <v>11</v>
       </c>
       <c r="E242" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F242" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G242" t="s">
         <v>15</v>
@@ -8781,10 +8781,10 @@
         <v>11</v>
       </c>
       <c r="E243" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F243" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G243" t="s">
         <v>14</v>
@@ -8813,10 +8813,10 @@
         <v>11</v>
       </c>
       <c r="E244" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F244" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G244" t="s">
         <v>14</v>
@@ -8845,10 +8845,10 @@
         <v>11</v>
       </c>
       <c r="E245" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F245" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G245" t="s">
         <v>15</v>
@@ -8877,10 +8877,10 @@
         <v>11</v>
       </c>
       <c r="E246" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F246" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G246" t="s">
         <v>14</v>
@@ -8909,10 +8909,10 @@
         <v>11</v>
       </c>
       <c r="E247" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F247" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G247" t="s">
         <v>15</v>
@@ -8944,7 +8944,7 @@
         <v>18</v>
       </c>
       <c r="F248" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G248" t="s">
         <v>15</v>
@@ -8973,7 +8973,7 @@
         <v>11</v>
       </c>
       <c r="E249" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F249" t="s">
         <v>18</v>
@@ -9005,10 +9005,10 @@
         <v>11</v>
       </c>
       <c r="E250" t="s">
+        <v>20</v>
+      </c>
+      <c r="F250" t="s">
         <v>21</v>
-      </c>
-      <c r="F250" t="s">
-        <v>22</v>
       </c>
       <c r="G250" t="s">
         <v>15</v>
@@ -9037,10 +9037,10 @@
         <v>11</v>
       </c>
       <c r="E251" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F251" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G251" t="s">
         <v>14</v>
@@ -9069,7 +9069,7 @@
         <v>11</v>
       </c>
       <c r="E252" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F252" t="s">
         <v>13</v>
@@ -9104,7 +9104,7 @@
         <v>13</v>
       </c>
       <c r="F253" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G253" t="s">
         <v>14</v>
@@ -9133,10 +9133,10 @@
         <v>11</v>
       </c>
       <c r="E254" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F254" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G254" t="s">
         <v>15</v>
@@ -9165,10 +9165,10 @@
         <v>11</v>
       </c>
       <c r="E255" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F255" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G255" t="s">
         <v>14</v>
@@ -9197,7 +9197,7 @@
         <v>11</v>
       </c>
       <c r="E256" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F256" t="s">
         <v>19</v>
@@ -9232,7 +9232,7 @@
         <v>19</v>
       </c>
       <c r="F257" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G257" t="s">
         <v>14</v>
@@ -9261,7 +9261,7 @@
         <v>11</v>
       </c>
       <c r="E258" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F258" t="s">
         <v>16</v>
@@ -9296,7 +9296,7 @@
         <v>16</v>
       </c>
       <c r="F259" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G259" t="s">
         <v>14</v>
@@ -9325,10 +9325,10 @@
         <v>11</v>
       </c>
       <c r="E260" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F260" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G260" t="s">
         <v>15</v>
@@ -9357,10 +9357,10 @@
         <v>11</v>
       </c>
       <c r="E261" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F261" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G261" t="s">
         <v>14</v>
@@ -9389,10 +9389,10 @@
         <v>11</v>
       </c>
       <c r="E262" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F262" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G262" t="s">
         <v>15</v>
@@ -9421,10 +9421,10 @@
         <v>11</v>
       </c>
       <c r="E263" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F263" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G263" t="s">
         <v>14</v>
@@ -9453,10 +9453,10 @@
         <v>11</v>
       </c>
       <c r="E264" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F264" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G264" t="s">
         <v>15</v>
@@ -9485,10 +9485,10 @@
         <v>11</v>
       </c>
       <c r="E265" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F265" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G265" t="s">
         <v>14</v>
@@ -9517,7 +9517,7 @@
         <v>11</v>
       </c>
       <c r="E266" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F266" t="s">
         <v>12</v>
@@ -9552,7 +9552,7 @@
         <v>12</v>
       </c>
       <c r="F267" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G267" t="s">
         <v>14</v>
@@ -9581,10 +9581,10 @@
         <v>11</v>
       </c>
       <c r="E268" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F268" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G268" t="s">
         <v>15</v>
@@ -9613,10 +9613,10 @@
         <v>11</v>
       </c>
       <c r="E269" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F269" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G269" t="s">
         <v>14</v>
@@ -9645,10 +9645,10 @@
         <v>11</v>
       </c>
       <c r="E270" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F270" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G270" t="s">
         <v>14</v>
@@ -9677,10 +9677,10 @@
         <v>11</v>
       </c>
       <c r="E271" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F271" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G271" t="s">
         <v>15</v>
@@ -9709,10 +9709,10 @@
         <v>11</v>
       </c>
       <c r="E272" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F272" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G272" t="s">
         <v>15</v>
@@ -9741,10 +9741,10 @@
         <v>11</v>
       </c>
       <c r="E273" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F273" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G273" t="s">
         <v>14</v>
@@ -9776,7 +9776,7 @@
         <v>17</v>
       </c>
       <c r="F274" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G274" t="s">
         <v>14</v>
@@ -9805,7 +9805,7 @@
         <v>11</v>
       </c>
       <c r="E275" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F275" t="s">
         <v>17</v>
@@ -9837,7 +9837,7 @@
         <v>11</v>
       </c>
       <c r="E276" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F276" t="s">
         <v>18</v>
@@ -9872,7 +9872,7 @@
         <v>18</v>
       </c>
       <c r="F277" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G277" t="s">
         <v>14</v>
@@ -9904,7 +9904,7 @@
         <v>13</v>
       </c>
       <c r="F278" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G278" t="s">
         <v>15</v>
@@ -9933,7 +9933,7 @@
         <v>11</v>
       </c>
       <c r="E279" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F279" t="s">
         <v>13</v>
@@ -9965,10 +9965,10 @@
         <v>11</v>
       </c>
       <c r="E280" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F280" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G280" t="s">
         <v>14</v>
@@ -9997,10 +9997,10 @@
         <v>11</v>
       </c>
       <c r="E281" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F281" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G281" t="s">
         <v>15</v>
@@ -10029,10 +10029,10 @@
         <v>11</v>
       </c>
       <c r="E282" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F282" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G282" t="s">
         <v>15</v>
@@ -10061,10 +10061,10 @@
         <v>11</v>
       </c>
       <c r="E283" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F283" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G283" t="s">
         <v>14</v>
@@ -10093,10 +10093,10 @@
         <v>11</v>
       </c>
       <c r="E284" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F284" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G284" t="s">
         <v>15</v>
@@ -10125,10 +10125,10 @@
         <v>11</v>
       </c>
       <c r="E285" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F285" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G285" t="s">
         <v>14</v>
@@ -10160,7 +10160,7 @@
         <v>19</v>
       </c>
       <c r="F286" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G286" t="s">
         <v>15</v>
@@ -10189,7 +10189,7 @@
         <v>11</v>
       </c>
       <c r="E287" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F287" t="s">
         <v>19</v>
@@ -10221,10 +10221,10 @@
         <v>11</v>
       </c>
       <c r="E288" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F288" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G288" t="s">
         <v>14</v>
@@ -10253,10 +10253,10 @@
         <v>11</v>
       </c>
       <c r="E289" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F289" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G289" t="s">
         <v>15</v>
@@ -10288,7 +10288,7 @@
         <v>12</v>
       </c>
       <c r="F290" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G290" t="s">
         <v>15</v>
@@ -10317,7 +10317,7 @@
         <v>11</v>
       </c>
       <c r="E291" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F291" t="s">
         <v>12</v>
@@ -10349,10 +10349,10 @@
         <v>11</v>
       </c>
       <c r="E292" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F292" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G292" t="s">
         <v>15</v>
@@ -10381,10 +10381,10 @@
         <v>11</v>
       </c>
       <c r="E293" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F293" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G293" t="s">
         <v>14</v>
@@ -10416,7 +10416,7 @@
         <v>16</v>
       </c>
       <c r="F294" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G294" t="s">
         <v>14</v>
@@ -10445,7 +10445,7 @@
         <v>11</v>
       </c>
       <c r="E295" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F295" t="s">
         <v>16</v>
@@ -10477,10 +10477,10 @@
         <v>11</v>
       </c>
       <c r="E296" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F296" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G296" t="s">
         <v>14</v>
@@ -10509,10 +10509,10 @@
         <v>11</v>
       </c>
       <c r="E297" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F297" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G297" t="s">
         <v>15</v>
@@ -10541,10 +10541,10 @@
         <v>11</v>
       </c>
       <c r="E298" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F298" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G298" t="s">
         <v>15</v>
@@ -10573,10 +10573,10 @@
         <v>11</v>
       </c>
       <c r="E299" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F299" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G299" t="s">
         <v>14</v>
@@ -10608,7 +10608,7 @@
         <v>17</v>
       </c>
       <c r="F300" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G300" t="s">
         <v>14</v>
@@ -10637,7 +10637,7 @@
         <v>11</v>
       </c>
       <c r="E301" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F301" t="s">
         <v>17</v>
@@ -10672,7 +10672,7 @@
         <v>18</v>
       </c>
       <c r="F302" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G302" t="s">
         <v>14</v>
@@ -10701,7 +10701,7 @@
         <v>11</v>
       </c>
       <c r="E303" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F303" t="s">
         <v>18</v>
@@ -10733,10 +10733,10 @@
         <v>11</v>
       </c>
       <c r="E304" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F304" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G304" t="s">
         <v>15</v>
@@ -10765,10 +10765,10 @@
         <v>11</v>
       </c>
       <c r="E305" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F305" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G305" t="s">
         <v>14</v>
@@ -10797,10 +10797,10 @@
         <v>11</v>
       </c>
       <c r="E306" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F306" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G306" t="s">
         <v>14</v>
@@ -10829,10 +10829,10 @@
         <v>11</v>
       </c>
       <c r="E307" t="s">
+        <v>32</v>
+      </c>
+      <c r="F307" t="s">
         <v>34</v>
-      </c>
-      <c r="F307" t="s">
-        <v>36</v>
       </c>
       <c r="G307" t="s">
         <v>15</v>
@@ -10864,7 +10864,7 @@
         <v>16</v>
       </c>
       <c r="F308" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G308" t="s">
         <v>15</v>
@@ -10893,7 +10893,7 @@
         <v>11</v>
       </c>
       <c r="E309" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F309" t="s">
         <v>16</v>
@@ -10925,10 +10925,10 @@
         <v>11</v>
       </c>
       <c r="E310" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F310" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G310" t="s">
         <v>15</v>
@@ -10957,10 +10957,10 @@
         <v>11</v>
       </c>
       <c r="E311" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F311" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G311" t="s">
         <v>14</v>
@@ -10989,10 +10989,10 @@
         <v>11</v>
       </c>
       <c r="E312" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F312" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G312" t="s">
         <v>14</v>
@@ -11021,10 +11021,10 @@
         <v>11</v>
       </c>
       <c r="E313" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F313" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G313" t="s">
         <v>15</v>
@@ -11056,7 +11056,7 @@
         <v>19</v>
       </c>
       <c r="F314" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G314" t="s">
         <v>14</v>
@@ -11085,7 +11085,7 @@
         <v>11</v>
       </c>
       <c r="E315" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F315" t="s">
         <v>19</v>
@@ -11117,10 +11117,10 @@
         <v>11</v>
       </c>
       <c r="E316" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F316" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G316" t="s">
         <v>15</v>
@@ -11149,10 +11149,10 @@
         <v>11</v>
       </c>
       <c r="E317" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F317" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G317" t="s">
         <v>14</v>
@@ -11181,10 +11181,10 @@
         <v>11</v>
       </c>
       <c r="E318" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F318" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G318" t="s">
         <v>15</v>
@@ -11213,10 +11213,10 @@
         <v>11</v>
       </c>
       <c r="E319" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F319" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G319" t="s">
         <v>14</v>
@@ -11245,10 +11245,10 @@
         <v>11</v>
       </c>
       <c r="E320" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F320" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G320" t="s">
         <v>14</v>
@@ -11277,10 +11277,10 @@
         <v>11</v>
       </c>
       <c r="E321" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F321" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G321" t="s">
         <v>15</v>
@@ -11309,7 +11309,7 @@
         <v>11</v>
       </c>
       <c r="E322" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F322" t="s">
         <v>13</v>
@@ -11344,7 +11344,7 @@
         <v>13</v>
       </c>
       <c r="F323" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G323" t="s">
         <v>14</v>
@@ -11373,10 +11373,10 @@
         <v>11</v>
       </c>
       <c r="E324" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F324" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G324" t="s">
         <v>14</v>
@@ -11405,10 +11405,10 @@
         <v>11</v>
       </c>
       <c r="E325" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F325" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G325" t="s">
         <v>15</v>
@@ -11437,10 +11437,10 @@
         <v>11</v>
       </c>
       <c r="E326" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F326" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G326" t="s">
         <v>15</v>
@@ -11469,10 +11469,10 @@
         <v>11</v>
       </c>
       <c r="E327" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F327" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G327" t="s">
         <v>14</v>
@@ -11501,7 +11501,7 @@
         <v>11</v>
       </c>
       <c r="E328" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F328" t="s">
         <v>17</v>
@@ -11536,7 +11536,7 @@
         <v>17</v>
       </c>
       <c r="F329" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G329" t="s">
         <v>15</v>
@@ -11568,7 +11568,7 @@
         <v>18</v>
       </c>
       <c r="F330" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G330" t="s">
         <v>15</v>
@@ -11597,7 +11597,7 @@
         <v>11</v>
       </c>
       <c r="E331" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F331" t="s">
         <v>18</v>
@@ -11629,10 +11629,10 @@
         <v>11</v>
       </c>
       <c r="E332" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F332" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G332" t="s">
         <v>15</v>
@@ -11661,10 +11661,10 @@
         <v>11</v>
       </c>
       <c r="E333" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F333" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G333" t="s">
         <v>14</v>
@@ -11696,7 +11696,7 @@
         <v>13</v>
       </c>
       <c r="F334" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G334" t="s">
         <v>15</v>
@@ -11725,7 +11725,7 @@
         <v>11</v>
       </c>
       <c r="E335" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F335" t="s">
         <v>13</v>
@@ -11757,10 +11757,10 @@
         <v>11</v>
       </c>
       <c r="E336" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F336" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G336" t="s">
         <v>14</v>
@@ -11789,10 +11789,10 @@
         <v>11</v>
       </c>
       <c r="E337" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F337" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G337" t="s">
         <v>15</v>
@@ -11821,10 +11821,10 @@
         <v>11</v>
       </c>
       <c r="E338" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F338" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G338" t="s">
         <v>15</v>
@@ -11853,10 +11853,10 @@
         <v>11</v>
       </c>
       <c r="E339" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F339" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G339" t="s">
         <v>14</v>
@@ -11885,10 +11885,10 @@
         <v>11</v>
       </c>
       <c r="E340" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F340" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G340" t="s">
         <v>15</v>
@@ -11917,10 +11917,10 @@
         <v>11</v>
       </c>
       <c r="E341" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F341" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G341" t="s">
         <v>14</v>
@@ -11952,7 +11952,7 @@
         <v>19</v>
       </c>
       <c r="F342" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G342" t="s">
         <v>15</v>
@@ -11981,7 +11981,7 @@
         <v>11</v>
       </c>
       <c r="E343" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F343" t="s">
         <v>19</v>
@@ -12013,10 +12013,10 @@
         <v>11</v>
       </c>
       <c r="E344" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F344" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G344" t="s">
         <v>14</v>
@@ -12045,10 +12045,10 @@
         <v>11</v>
       </c>
       <c r="E345" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F345" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G345" t="s">
         <v>15</v>
@@ -12077,10 +12077,10 @@
         <v>11</v>
       </c>
       <c r="E346" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F346" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G346" t="s">
         <v>15</v>
@@ -12109,10 +12109,10 @@
         <v>11</v>
       </c>
       <c r="E347" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F347" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G347" t="s">
         <v>14</v>
@@ -12141,10 +12141,10 @@
         <v>11</v>
       </c>
       <c r="E348" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F348" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G348" t="s">
         <v>15</v>
@@ -12173,10 +12173,10 @@
         <v>11</v>
       </c>
       <c r="E349" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F349" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G349" t="s">
         <v>14</v>
@@ -12205,7 +12205,7 @@
         <v>11</v>
       </c>
       <c r="E350" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F350" t="s">
         <v>12</v>
@@ -12240,7 +12240,7 @@
         <v>12</v>
       </c>
       <c r="F351" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G351" t="s">
         <v>14</v>
@@ -12269,10 +12269,10 @@
         <v>11</v>
       </c>
       <c r="E352" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F352" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G352" t="s">
         <v>14</v>
@@ -12301,10 +12301,10 @@
         <v>11</v>
       </c>
       <c r="E353" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F353" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G353" t="s">
         <v>15</v>
@@ -12336,7 +12336,7 @@
         <v>13</v>
       </c>
       <c r="F354" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G354" t="s">
         <v>14</v>
@@ -12365,7 +12365,7 @@
         <v>11</v>
       </c>
       <c r="E355" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F355" t="s">
         <v>13</v>
@@ -12400,7 +12400,7 @@
         <v>18</v>
       </c>
       <c r="F356" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G356" t="s">
         <v>14</v>
@@ -12429,7 +12429,7 @@
         <v>11</v>
       </c>
       <c r="E357" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F357" t="s">
         <v>18</v>
@@ -12461,7 +12461,7 @@
         <v>11</v>
       </c>
       <c r="E358" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F358" t="s">
         <v>17</v>
@@ -12496,7 +12496,7 @@
         <v>17</v>
       </c>
       <c r="F359" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G359" t="s">
         <v>15</v>
@@ -12525,10 +12525,10 @@
         <v>11</v>
       </c>
       <c r="E360" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F360" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G360" t="s">
         <v>14</v>
@@ -12557,10 +12557,10 @@
         <v>11</v>
       </c>
       <c r="E361" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F361" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G361" t="s">
         <v>15</v>
@@ -12589,7 +12589,7 @@
         <v>11</v>
       </c>
       <c r="E362" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F362" t="s">
         <v>19</v>
@@ -12624,7 +12624,7 @@
         <v>19</v>
       </c>
       <c r="F363" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G363" t="s">
         <v>14</v>
@@ -12653,10 +12653,10 @@
         <v>11</v>
       </c>
       <c r="E364" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F364" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G364" t="s">
         <v>15</v>
@@ -12685,10 +12685,10 @@
         <v>11</v>
       </c>
       <c r="E365" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F365" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G365" t="s">
         <v>14</v>
@@ -12717,10 +12717,10 @@
         <v>11</v>
       </c>
       <c r="E366" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F366" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G366" t="s">
         <v>14</v>
@@ -12749,10 +12749,10 @@
         <v>11</v>
       </c>
       <c r="E367" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F367" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G367" t="s">
         <v>15</v>
@@ -12784,7 +12784,7 @@
         <v>12</v>
       </c>
       <c r="F368" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G368" t="s">
         <v>14</v>
@@ -12813,7 +12813,7 @@
         <v>11</v>
       </c>
       <c r="E369" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F369" t="s">
         <v>12</v>
@@ -12845,10 +12845,10 @@
         <v>11</v>
       </c>
       <c r="E370" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F370" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G370" t="s">
         <v>14</v>
@@ -12877,10 +12877,10 @@
         <v>11</v>
       </c>
       <c r="E371" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F371" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G371" t="s">
         <v>15</v>
@@ -12909,10 +12909,10 @@
         <v>11</v>
       </c>
       <c r="E372" t="s">
+        <v>26</v>
+      </c>
+      <c r="F372" t="s">
         <v>27</v>
-      </c>
-      <c r="F372" t="s">
-        <v>28</v>
       </c>
       <c r="G372" t="s">
         <v>15</v>
@@ -12941,10 +12941,10 @@
         <v>11</v>
       </c>
       <c r="E373" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F373" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G373" t="s">
         <v>14</v>
@@ -12973,10 +12973,10 @@
         <v>11</v>
       </c>
       <c r="E374" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F374" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G374" t="s">
         <v>15</v>
@@ -13005,10 +13005,10 @@
         <v>11</v>
       </c>
       <c r="E375" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F375" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G375" t="s">
         <v>14</v>
@@ -13037,10 +13037,10 @@
         <v>11</v>
       </c>
       <c r="E376" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F376" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G376" t="s">
         <v>14</v>
@@ -13069,10 +13069,10 @@
         <v>11</v>
       </c>
       <c r="E377" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F377" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G377" t="s">
         <v>15</v>
@@ -13101,10 +13101,10 @@
         <v>11</v>
       </c>
       <c r="E378" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F378" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G378" t="s">
         <v>15</v>
@@ -13133,10 +13133,10 @@
         <v>11</v>
       </c>
       <c r="E379" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F379" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G379" t="s">
         <v>14</v>
@@ -13165,10 +13165,10 @@
         <v>11</v>
       </c>
       <c r="E380" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F380" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G380" t="s">
         <v>15</v>
@@ -13197,10 +13197,10 @@
         <v>11</v>
       </c>
       <c r="E381" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F381" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G381" t="s">
         <v>14</v>
@@ -13229,10 +13229,10 @@
         <v>11</v>
       </c>
       <c r="E382" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F382" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G382" t="s">
         <v>15</v>
@@ -13261,10 +13261,10 @@
         <v>11</v>
       </c>
       <c r="E383" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F383" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G383" t="s">
         <v>14</v>
@@ -13293,7 +13293,7 @@
         <v>11</v>
       </c>
       <c r="E384" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F384" t="s">
         <v>16</v>
@@ -13328,7 +13328,7 @@
         <v>16</v>
       </c>
       <c r="F385" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G385" t="s">
         <v>14</v>
@@ -13360,7 +13360,7 @@
         <v>13</v>
       </c>
       <c r="F386" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G386" t="s">
         <v>15</v>
@@ -13389,7 +13389,7 @@
         <v>11</v>
       </c>
       <c r="E387" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F387" t="s">
         <v>13</v>
@@ -13424,7 +13424,7 @@
         <v>17</v>
       </c>
       <c r="F388" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G388" t="s">
         <v>15</v>
@@ -13453,7 +13453,7 @@
         <v>11</v>
       </c>
       <c r="E389" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F389" t="s">
         <v>17</v>
@@ -13485,7 +13485,7 @@
         <v>11</v>
       </c>
       <c r="E390" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F390" t="s">
         <v>18</v>
@@ -13520,7 +13520,7 @@
         <v>18</v>
       </c>
       <c r="F391" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G391" t="s">
         <v>15</v>
@@ -13549,10 +13549,10 @@
         <v>11</v>
       </c>
       <c r="E392" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F392" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G392" t="s">
         <v>15</v>
@@ -13581,10 +13581,10 @@
         <v>11</v>
       </c>
       <c r="E393" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F393" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G393" t="s">
         <v>14</v>
@@ -13613,10 +13613,10 @@
         <v>11</v>
       </c>
       <c r="E394" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F394" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G394" t="s">
         <v>15</v>
@@ -13645,10 +13645,10 @@
         <v>11</v>
       </c>
       <c r="E395" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F395" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G395" t="s">
         <v>14</v>
@@ -13677,10 +13677,10 @@
         <v>11</v>
       </c>
       <c r="E396" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F396" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G396" t="s">
         <v>14</v>
@@ -13709,10 +13709,10 @@
         <v>11</v>
       </c>
       <c r="E397" t="s">
+        <v>41</v>
+      </c>
+      <c r="F397" t="s">
         <v>43</v>
-      </c>
-      <c r="F397" t="s">
-        <v>45</v>
       </c>
       <c r="G397" t="s">
         <v>15</v>
@@ -13744,7 +13744,7 @@
         <v>16</v>
       </c>
       <c r="F398" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G398" t="s">
         <v>15</v>
@@ -13773,7 +13773,7 @@
         <v>11</v>
       </c>
       <c r="E399" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F399" t="s">
         <v>16</v>
@@ -13808,7 +13808,7 @@
         <v>12</v>
       </c>
       <c r="F400" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G400" t="s">
         <v>15</v>
@@ -13837,7 +13837,7 @@
         <v>11</v>
       </c>
       <c r="E401" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F401" t="s">
         <v>12</v>
@@ -13872,7 +13872,7 @@
         <v>19</v>
       </c>
       <c r="F402" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G402" t="s">
         <v>15</v>
@@ -13901,7 +13901,7 @@
         <v>11</v>
       </c>
       <c r="E403" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F403" t="s">
         <v>19</v>
@@ -13933,10 +13933,10 @@
         <v>11</v>
       </c>
       <c r="E404" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F404" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G404" t="s">
         <v>14</v>
@@ -13965,10 +13965,10 @@
         <v>11</v>
       </c>
       <c r="E405" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F405" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G405" t="s">
         <v>15</v>
@@ -13997,10 +13997,10 @@
         <v>11</v>
       </c>
       <c r="E406" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F406" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G406" t="s">
         <v>14</v>
@@ -14029,10 +14029,10 @@
         <v>11</v>
       </c>
       <c r="E407" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F407" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G407" t="s">
         <v>15</v>
@@ -14061,10 +14061,10 @@
         <v>11</v>
       </c>
       <c r="E408" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F408" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G408" t="s">
         <v>14</v>
@@ -14093,10 +14093,10 @@
         <v>11</v>
       </c>
       <c r="E409" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F409" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G409" t="s">
         <v>15</v>
@@ -14125,10 +14125,10 @@
         <v>11</v>
       </c>
       <c r="E410" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F410" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G410" t="s">
         <v>14</v>
@@ -14157,10 +14157,10 @@
         <v>11</v>
       </c>
       <c r="E411" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F411" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G411" t="s">
         <v>15</v>
@@ -14189,10 +14189,10 @@
         <v>11</v>
       </c>
       <c r="E412" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F412" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G412" t="s">
         <v>14</v>
@@ -14221,10 +14221,10 @@
         <v>11</v>
       </c>
       <c r="E413" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F413" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G413" t="s">
         <v>15</v>
@@ -14253,10 +14253,10 @@
         <v>11</v>
       </c>
       <c r="E414" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F414" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G414" t="s">
         <v>15</v>
@@ -14285,10 +14285,10 @@
         <v>11</v>
       </c>
       <c r="E415" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F415" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G415" t="s">
         <v>14</v>
@@ -14317,10 +14317,10 @@
         <v>11</v>
       </c>
       <c r="E416" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F416" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G416" t="s">
         <v>15</v>
@@ -14349,10 +14349,10 @@
         <v>11</v>
       </c>
       <c r="E417" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F417" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G417" t="s">
         <v>14</v>
@@ -14381,7 +14381,7 @@
         <v>11</v>
       </c>
       <c r="E418" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F418" t="s">
         <v>19</v>
@@ -14416,7 +14416,7 @@
         <v>19</v>
       </c>
       <c r="F419" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G419" t="s">
         <v>14</v>
@@ -14445,10 +14445,10 @@
         <v>11</v>
       </c>
       <c r="E420" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F420" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G420" t="s">
         <v>14</v>
@@ -14477,10 +14477,10 @@
         <v>11</v>
       </c>
       <c r="E421" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F421" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G421" t="s">
         <v>15</v>
@@ -14573,10 +14573,10 @@
         <v>11</v>
       </c>
       <c r="E424" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F424" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G424" t="s">
         <v>14</v>
@@ -14605,10 +14605,10 @@
         <v>11</v>
       </c>
       <c r="E425" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F425" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G425" t="s">
         <v>15</v>
@@ -14637,10 +14637,10 @@
         <v>11</v>
       </c>
       <c r="E426" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F426" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G426" t="s">
         <v>15</v>
@@ -14669,10 +14669,10 @@
         <v>11</v>
       </c>
       <c r="E427" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F427" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G427" t="s">
         <v>14</v>
@@ -14701,10 +14701,10 @@
         <v>11</v>
       </c>
       <c r="E428" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F428" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G428" t="s">
         <v>14</v>
@@ -14733,10 +14733,10 @@
         <v>11</v>
       </c>
       <c r="E429" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F429" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G429" t="s">
         <v>15</v>
@@ -14765,10 +14765,10 @@
         <v>11</v>
       </c>
       <c r="E430" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F430" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G430" t="s">
         <v>14</v>
@@ -14797,10 +14797,10 @@
         <v>11</v>
       </c>
       <c r="E431" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F431" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G431" t="s">
         <v>15</v>
@@ -14829,10 +14829,10 @@
         <v>11</v>
       </c>
       <c r="E432" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F432" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G432" t="s">
         <v>15</v>
@@ -14861,10 +14861,10 @@
         <v>11</v>
       </c>
       <c r="E433" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F433" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G433" t="s">
         <v>14</v>
@@ -14893,10 +14893,10 @@
         <v>11</v>
       </c>
       <c r="E434" t="s">
+        <v>27</v>
+      </c>
+      <c r="F434" t="s">
         <v>28</v>
-      </c>
-      <c r="F434" t="s">
-        <v>29</v>
       </c>
       <c r="G434" t="s">
         <v>14</v>
@@ -14925,10 +14925,10 @@
         <v>11</v>
       </c>
       <c r="E435" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F435" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G435" t="s">
         <v>15</v>
@@ -14957,10 +14957,10 @@
         <v>11</v>
       </c>
       <c r="E436" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F436" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G436" t="s">
         <v>15</v>
@@ -14989,10 +14989,10 @@
         <v>11</v>
       </c>
       <c r="E437" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F437" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G437" t="s">
         <v>14</v>
@@ -15021,10 +15021,10 @@
         <v>11</v>
       </c>
       <c r="E438" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F438" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G438" t="s">
         <v>14</v>
@@ -15053,10 +15053,10 @@
         <v>11</v>
       </c>
       <c r="E439" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F439" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G439" t="s">
         <v>15</v>
@@ -15088,7 +15088,7 @@
         <v>16</v>
       </c>
       <c r="F440" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G440" t="s">
         <v>14</v>
@@ -15117,7 +15117,7 @@
         <v>11</v>
       </c>
       <c r="E441" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F441" t="s">
         <v>16</v>
@@ -15152,7 +15152,7 @@
         <v>17</v>
       </c>
       <c r="F442" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G442" t="s">
         <v>14</v>
@@ -15181,7 +15181,7 @@
         <v>11</v>
       </c>
       <c r="E443" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F443" t="s">
         <v>17</v>
@@ -15213,10 +15213,10 @@
         <v>11</v>
       </c>
       <c r="E444" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F444" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G444" t="s">
         <v>15</v>
@@ -15245,10 +15245,10 @@
         <v>11</v>
       </c>
       <c r="E445" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F445" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G445" t="s">
         <v>14</v>
@@ -15280,7 +15280,7 @@
         <v>18</v>
       </c>
       <c r="F446" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G446" t="s">
         <v>14</v>
@@ -15309,7 +15309,7 @@
         <v>11</v>
       </c>
       <c r="E447" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F447" t="s">
         <v>18</v>
@@ -15341,10 +15341,10 @@
         <v>11</v>
       </c>
       <c r="E448" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F448" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G448" t="s">
         <v>15</v>
@@ -15373,10 +15373,10 @@
         <v>11</v>
       </c>
       <c r="E449" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F449" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G449" t="s">
         <v>14</v>
@@ -15405,10 +15405,10 @@
         <v>11</v>
       </c>
       <c r="E450" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F450" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G450" t="s">
         <v>14</v>
@@ -15437,10 +15437,10 @@
         <v>11</v>
       </c>
       <c r="E451" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F451" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G451" t="s">
         <v>15</v>
@@ -15469,7 +15469,7 @@
         <v>11</v>
       </c>
       <c r="E452" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F452" t="s">
         <v>18</v>
@@ -15504,7 +15504,7 @@
         <v>18</v>
       </c>
       <c r="F453" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G453" t="s">
         <v>14</v>
@@ -15533,10 +15533,10 @@
         <v>11</v>
       </c>
       <c r="E454" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F454" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G454" t="s">
         <v>15</v>
@@ -15565,10 +15565,10 @@
         <v>11</v>
       </c>
       <c r="E455" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F455" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G455" t="s">
         <v>14</v>
@@ -15600,7 +15600,7 @@
         <v>17</v>
       </c>
       <c r="F456" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G456" t="s">
         <v>15</v>
@@ -15629,7 +15629,7 @@
         <v>11</v>
       </c>
       <c r="E457" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F457" t="s">
         <v>17</v>
@@ -15661,10 +15661,10 @@
         <v>11</v>
       </c>
       <c r="E458" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F458" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G458" t="s">
         <v>15</v>
@@ -15693,10 +15693,10 @@
         <v>11</v>
       </c>
       <c r="E459" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F459" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G459" t="s">
         <v>14</v>
@@ -15725,10 +15725,10 @@
         <v>11</v>
       </c>
       <c r="E460" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F460" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G460" t="s">
         <v>15</v>
@@ -15757,10 +15757,10 @@
         <v>11</v>
       </c>
       <c r="E461" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F461" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G461" t="s">
         <v>14</v>
@@ -15789,10 +15789,10 @@
         <v>11</v>
       </c>
       <c r="E462" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F462" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G462" t="s">
         <v>14</v>
@@ -15821,10 +15821,10 @@
         <v>11</v>
       </c>
       <c r="E463" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F463" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G463" t="s">
         <v>15</v>
@@ -15853,10 +15853,10 @@
         <v>11</v>
       </c>
       <c r="E464" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F464" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G464" t="s">
         <v>14</v>
@@ -15885,10 +15885,10 @@
         <v>11</v>
       </c>
       <c r="E465" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F465" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G465" t="s">
         <v>15</v>
@@ -15917,10 +15917,10 @@
         <v>11</v>
       </c>
       <c r="E466" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F466" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G466" t="s">
         <v>14</v>
@@ -15949,10 +15949,10 @@
         <v>11</v>
       </c>
       <c r="E467" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F467" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G467" t="s">
         <v>15</v>
@@ -15984,7 +15984,7 @@
         <v>19</v>
       </c>
       <c r="F468" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G468" t="s">
         <v>15</v>
@@ -16013,7 +16013,7 @@
         <v>11</v>
       </c>
       <c r="E469" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F469" t="s">
         <v>19</v>
@@ -16045,10 +16045,10 @@
         <v>11</v>
       </c>
       <c r="E470" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F470" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G470" t="s">
         <v>15</v>
@@ -16077,10 +16077,10 @@
         <v>11</v>
       </c>
       <c r="E471" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F471" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G471" t="s">
         <v>14</v>
@@ -16109,10 +16109,10 @@
         <v>11</v>
       </c>
       <c r="E472" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F472" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G472" t="s">
         <v>14</v>
@@ -16141,10 +16141,10 @@
         <v>11</v>
       </c>
       <c r="E473" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F473" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G473" t="s">
         <v>15</v>
@@ -16173,10 +16173,10 @@
         <v>11</v>
       </c>
       <c r="E474" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F474" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G474" t="s">
         <v>14</v>
@@ -16205,10 +16205,10 @@
         <v>11</v>
       </c>
       <c r="E475" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F475" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G475" t="s">
         <v>15</v>
@@ -16237,10 +16237,10 @@
         <v>11</v>
       </c>
       <c r="E476" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F476" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G476" t="s">
         <v>15</v>
@@ -16269,10 +16269,10 @@
         <v>11</v>
       </c>
       <c r="E477" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F477" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G477" t="s">
         <v>14</v>
@@ -16301,7 +16301,7 @@
         <v>11</v>
       </c>
       <c r="E478" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F478" t="s">
         <v>13</v>
@@ -16336,7 +16336,7 @@
         <v>13</v>
       </c>
       <c r="F479" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G479" t="s">
         <v>15</v>
@@ -16432,7 +16432,7 @@
         <v>17</v>
       </c>
       <c r="F482" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G482" t="s">
         <v>14</v>
@@ -16461,7 +16461,7 @@
         <v>11</v>
       </c>
       <c r="E483" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F483" t="s">
         <v>17</v>
@@ -16557,10 +16557,10 @@
         <v>11</v>
       </c>
       <c r="E486" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F486" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G486" t="s">
         <v>14</v>
@@ -16589,10 +16589,10 @@
         <v>11</v>
       </c>
       <c r="E487" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F487" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G487" t="s">
         <v>15</v>
@@ -16685,10 +16685,10 @@
         <v>11</v>
       </c>
       <c r="E490" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F490" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G490" t="s">
         <v>15</v>
@@ -16717,10 +16717,10 @@
         <v>11</v>
       </c>
       <c r="E491" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F491" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G491" t="s">
         <v>14</v>
@@ -16752,7 +16752,7 @@
         <v>12</v>
       </c>
       <c r="F492" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G492" t="s">
         <v>14</v>
@@ -16781,7 +16781,7 @@
         <v>11</v>
       </c>
       <c r="E493" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F493" t="s">
         <v>12</v>
@@ -16813,10 +16813,10 @@
         <v>11</v>
       </c>
       <c r="E494" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F494" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G494" t="s">
         <v>15</v>
@@ -16845,10 +16845,10 @@
         <v>11</v>
       </c>
       <c r="E495" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F495" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G495" t="s">
         <v>14</v>
@@ -16877,10 +16877,10 @@
         <v>11</v>
       </c>
       <c r="E496" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F496" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G496" t="s">
         <v>14</v>
@@ -16909,10 +16909,10 @@
         <v>11</v>
       </c>
       <c r="E497" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F497" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G497" t="s">
         <v>15</v>
@@ -16941,10 +16941,10 @@
         <v>11</v>
       </c>
       <c r="E498" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F498" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G498" t="s">
         <v>15</v>
@@ -16973,10 +16973,10 @@
         <v>11</v>
       </c>
       <c r="E499" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F499" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G499" t="s">
         <v>14</v>
@@ -17005,10 +17005,10 @@
         <v>11</v>
       </c>
       <c r="E500" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F500" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G500" t="s">
         <v>15</v>
@@ -17037,10 +17037,10 @@
         <v>11</v>
       </c>
       <c r="E501" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F501" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G501" t="s">
         <v>14</v>
@@ -17069,10 +17069,10 @@
         <v>11</v>
       </c>
       <c r="E502" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F502" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G502" t="s">
         <v>15</v>
@@ -17101,10 +17101,10 @@
         <v>11</v>
       </c>
       <c r="E503" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F503" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G503" t="s">
         <v>14</v>
@@ -17133,10 +17133,10 @@
         <v>11</v>
       </c>
       <c r="E504" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F504" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G504" t="s">
         <v>15</v>
@@ -17165,10 +17165,10 @@
         <v>11</v>
       </c>
       <c r="E505" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F505" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G505" t="s">
         <v>14</v>
@@ -17197,10 +17197,10 @@
         <v>11</v>
       </c>
       <c r="E506" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F506" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G506" t="s">
         <v>14</v>
@@ -17229,10 +17229,10 @@
         <v>11</v>
       </c>
       <c r="E507" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F507" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G507" t="s">
         <v>15</v>
@@ -17261,10 +17261,10 @@
         <v>11</v>
       </c>
       <c r="E508" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F508" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G508" t="s">
         <v>14</v>
@@ -17293,10 +17293,10 @@
         <v>11</v>
       </c>
       <c r="E509" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F509" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G509" t="s">
         <v>15</v>
@@ -17325,10 +17325,10 @@
         <v>11</v>
       </c>
       <c r="E510" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F510" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G510" t="s">
         <v>15</v>
@@ -17357,10 +17357,10 @@
         <v>11</v>
       </c>
       <c r="E511" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F511" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G511" t="s">
         <v>14</v>
@@ -17389,10 +17389,10 @@
         <v>11</v>
       </c>
       <c r="E512" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F512" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G512" t="s">
         <v>14</v>
@@ -17421,10 +17421,10 @@
         <v>11</v>
       </c>
       <c r="E513" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F513" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G513" t="s">
         <v>15</v>
@@ -17447,13 +17447,13 @@
         <v>2019</v>
       </c>
       <c r="C514" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D514" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E514" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F514" t="s">
         <v>18</v>
@@ -17479,16 +17479,16 @@
         <v>2019</v>
       </c>
       <c r="C515" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D515" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E515" t="s">
         <v>18</v>
       </c>
       <c r="F515" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G515" t="s">
         <v>14</v>
@@ -17511,16 +17511,16 @@
         <v>2019</v>
       </c>
       <c r="C516" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D516" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E516" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F516" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G516" t="s">
         <v>14</v>
@@ -17543,16 +17543,16 @@
         <v>2019</v>
       </c>
       <c r="C517" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D517" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E517" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F517" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G517" t="s">
         <v>15</v>
@@ -17575,16 +17575,16 @@
         <v>2019</v>
       </c>
       <c r="C518" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D518" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E518" t="s">
         <v>16</v>
       </c>
       <c r="F518" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G518" t="s">
         <v>14</v>
@@ -17607,13 +17607,13 @@
         <v>2019</v>
       </c>
       <c r="C519" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D519" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E519" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F519" t="s">
         <v>16</v>
@@ -17639,16 +17639,16 @@
         <v>2019</v>
       </c>
       <c r="C520" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D520" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E520" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F520" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G520" t="s">
         <v>14</v>
@@ -17671,16 +17671,16 @@
         <v>2019</v>
       </c>
       <c r="C521" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D521" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E521" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F521" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G521" t="s">
         <v>15</v>
@@ -17703,13 +17703,13 @@
         <v>2019</v>
       </c>
       <c r="C522" t="s">
+        <v>44</v>
+      </c>
+      <c r="D522" t="s">
         <v>46</v>
       </c>
-      <c r="D522" t="s">
-        <v>48</v>
-      </c>
       <c r="E522" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F522" t="s">
         <v>16</v>
@@ -17735,16 +17735,16 @@
         <v>2019</v>
       </c>
       <c r="C523" t="s">
+        <v>44</v>
+      </c>
+      <c r="D523" t="s">
         <v>46</v>
-      </c>
-      <c r="D523" t="s">
-        <v>48</v>
       </c>
       <c r="E523" t="s">
         <v>16</v>
       </c>
       <c r="F523" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G523" t="s">
         <v>14</v>
@@ -17767,16 +17767,16 @@
         <v>2019</v>
       </c>
       <c r="C524" t="s">
+        <v>44</v>
+      </c>
+      <c r="D524" t="s">
         <v>46</v>
       </c>
-      <c r="D524" t="s">
-        <v>48</v>
-      </c>
       <c r="E524" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F524" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G524" t="s">
         <v>14</v>
@@ -17799,16 +17799,16 @@
         <v>2019</v>
       </c>
       <c r="C525" t="s">
+        <v>44</v>
+      </c>
+      <c r="D525" t="s">
         <v>46</v>
       </c>
-      <c r="D525" t="s">
-        <v>48</v>
-      </c>
       <c r="E525" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F525" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G525" t="s">
         <v>15</v>
@@ -17831,16 +17831,16 @@
         <v>2019</v>
       </c>
       <c r="C526" t="s">
+        <v>44</v>
+      </c>
+      <c r="D526" t="s">
         <v>46</v>
       </c>
-      <c r="D526" t="s">
-        <v>48</v>
-      </c>
       <c r="E526" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F526" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G526" t="s">
         <v>15</v>
@@ -17863,16 +17863,16 @@
         <v>2019</v>
       </c>
       <c r="C527" t="s">
+        <v>44</v>
+      </c>
+      <c r="D527" t="s">
         <v>46</v>
       </c>
-      <c r="D527" t="s">
-        <v>48</v>
-      </c>
       <c r="E527" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F527" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G527" t="s">
         <v>14</v>
@@ -17895,16 +17895,16 @@
         <v>2019</v>
       </c>
       <c r="C528" t="s">
+        <v>44</v>
+      </c>
+      <c r="D528" t="s">
         <v>46</v>
-      </c>
-      <c r="D528" t="s">
-        <v>48</v>
       </c>
       <c r="E528" t="s">
         <v>12</v>
       </c>
       <c r="F528" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G528" t="s">
         <v>15</v>
@@ -17927,13 +17927,13 @@
         <v>2019</v>
       </c>
       <c r="C529" t="s">
+        <v>44</v>
+      </c>
+      <c r="D529" t="s">
         <v>46</v>
       </c>
-      <c r="D529" t="s">
-        <v>48</v>
-      </c>
       <c r="E529" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F529" t="s">
         <v>12</v>
@@ -17959,16 +17959,16 @@
         <v>2019</v>
       </c>
       <c r="C530" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D530" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E530" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F530" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G530" t="s">
         <v>15</v>
@@ -17991,16 +17991,16 @@
         <v>2019</v>
       </c>
       <c r="C531" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D531" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E531" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F531" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G531" t="s">
         <v>14</v>
@@ -18023,13 +18023,13 @@
         <v>2019</v>
       </c>
       <c r="C532" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D532" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E532" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F532" t="s">
         <v>12</v>
@@ -18055,16 +18055,16 @@
         <v>2019</v>
       </c>
       <c r="C533" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D533" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E533" t="s">
         <v>12</v>
       </c>
       <c r="F533" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G533" t="s">
         <v>14</v>
@@ -18087,19 +18087,19 @@
         <v>2019</v>
       </c>
       <c r="C534" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D534" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E534" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F534" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G534" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H534">
         <v>31</v>
@@ -18119,19 +18119,19 @@
         <v>2019</v>
       </c>
       <c r="C535" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D535" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E535" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F535" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G535" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H535">
         <v>20</v>
